--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.056722717920412</v>
+        <v>1.471717441662067</v>
       </c>
       <c r="D2" t="n">
-        <v>8.729314710326422</v>
+        <v>1.418513640428044</v>
       </c>
       <c r="E2" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F2" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.23272690859139</v>
+        <v>2.475318122646101</v>
       </c>
       <c r="D3" t="n">
-        <v>24.84106419380215</v>
+        <v>4.03667293149285</v>
       </c>
       <c r="E3" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F3" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.704616220884152</v>
+        <v>1.252000135893675</v>
       </c>
       <c r="D4" t="n">
-        <v>17.83420069344951</v>
+        <v>2.898057612685546</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F4" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.18117746111953</v>
+        <v>2.141941337431924</v>
       </c>
       <c r="D5" t="n">
-        <v>14.13473576293676</v>
+        <v>2.296894561477223</v>
       </c>
       <c r="E5" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F5" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.555388988314105</v>
+        <v>1.227750710601042</v>
       </c>
       <c r="D6" t="n">
-        <v>7.254957718561981</v>
+        <v>1.178930629266322</v>
       </c>
       <c r="E6" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F6" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.35041058811376</v>
+        <v>1.681941720568487</v>
       </c>
       <c r="D7" t="n">
-        <v>3.984064622852797</v>
+        <v>0.6474105012135796</v>
       </c>
       <c r="E7" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F7" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.977133359888436</v>
+        <v>1.296284170981871</v>
       </c>
       <c r="D8" t="n">
-        <v>4.96520320973335</v>
+        <v>0.8068455215816693</v>
       </c>
       <c r="E8" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F8" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.09593519916139</v>
+        <v>6.840589469863726</v>
       </c>
       <c r="D9" t="n">
-        <v>35.86796555476462</v>
+        <v>5.828544402649252</v>
       </c>
       <c r="E9" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F9" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.25612999755953</v>
+        <v>5.241621124603425</v>
       </c>
       <c r="D10" t="n">
-        <v>25.30577068927809</v>
+        <v>4.11218773700769</v>
       </c>
       <c r="E10" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F10" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.61758758555382</v>
+        <v>2.212857982652496</v>
       </c>
       <c r="D11" t="n">
-        <v>5.512829530974602</v>
+        <v>0.8958347987833729</v>
       </c>
       <c r="E11" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F11" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.91870848427711</v>
+        <v>2.586790128695031</v>
       </c>
       <c r="D12" t="n">
-        <v>7.584711910369732</v>
+        <v>1.232515685435081</v>
       </c>
       <c r="E12" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F12" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.03200870847213</v>
+        <v>1.955201415126721</v>
       </c>
       <c r="D13" t="n">
-        <v>11.81377890791291</v>
+        <v>1.919739072535848</v>
       </c>
       <c r="E13" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F13" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.70313291398084</v>
+        <v>5.801759098521887</v>
       </c>
       <c r="D14" t="n">
-        <v>28.85521438940832</v>
+        <v>4.688972338278853</v>
       </c>
       <c r="E14" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F14" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.66840551826112</v>
+        <v>2.058615896717432</v>
       </c>
       <c r="D15" t="n">
-        <v>12.58166407118269</v>
+        <v>2.044520411567188</v>
       </c>
       <c r="E15" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F15" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.42541832860392</v>
+        <v>1.531630478398137</v>
       </c>
       <c r="D16" t="n">
-        <v>9.600617353406459</v>
+        <v>1.56010031992855</v>
       </c>
       <c r="E16" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F16" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>13.07889044208034</v>
+        <v>2.125319696838055</v>
       </c>
       <c r="D17" t="n">
-        <v>7.740235306730041</v>
+        <v>1.257788237343632</v>
       </c>
       <c r="E17" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F17" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>19.90272923875292</v>
+        <v>3.23419350129735</v>
       </c>
       <c r="D18" t="n">
-        <v>19.9692031836213</v>
+        <v>3.244995517338462</v>
       </c>
       <c r="E18" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F18" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24.09512200398269</v>
+        <v>3.915457325647187</v>
       </c>
       <c r="D19" t="n">
-        <v>23.23805922295802</v>
+        <v>3.776184623730678</v>
       </c>
       <c r="E19" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F19" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>24.33546828588427</v>
+        <v>3.954513596456194</v>
       </c>
       <c r="D20" t="n">
-        <v>24.54249153210745</v>
+        <v>3.988154873967461</v>
       </c>
       <c r="E20" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F20" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>15.08684417586353</v>
+        <v>2.451612178577823</v>
       </c>
       <c r="D21" t="n">
-        <v>16.41357016465287</v>
+        <v>2.667205151756092</v>
       </c>
       <c r="E21" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F21" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>26.69345084282095</v>
+        <v>4.337685761958404</v>
       </c>
       <c r="D22" t="n">
-        <v>26.7155905697863</v>
+        <v>4.341283467590275</v>
       </c>
       <c r="E22" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F22" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>8.011832247991588</v>
+        <v>1.301922740298633</v>
       </c>
       <c r="D23" t="n">
-        <v>6.595652692437239</v>
+        <v>1.071793562521051</v>
       </c>
       <c r="E23" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F23" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>40.82392561940372</v>
+        <v>6.633887913153106</v>
       </c>
       <c r="D24" t="n">
-        <v>39.17514707553332</v>
+        <v>6.365961399774165</v>
       </c>
       <c r="E24" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F24" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>19.56318453166043</v>
+        <v>3.17901748639482</v>
       </c>
       <c r="D25" t="n">
-        <v>20.5017166217973</v>
+        <v>3.331528951042061</v>
       </c>
       <c r="E25" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F25" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>35.55300416845044</v>
+        <v>5.777363177373197</v>
       </c>
       <c r="D26" t="n">
-        <v>35.77832384622059</v>
+        <v>5.813977625010847</v>
       </c>
       <c r="E26" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F26" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>27.84924247940349</v>
+        <v>4.525501902903068</v>
       </c>
       <c r="D27" t="n">
-        <v>27.05125206882411</v>
+        <v>4.395828461183918</v>
       </c>
       <c r="E27" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F27" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>47.57542183386696</v>
+        <v>7.731006048003382</v>
       </c>
       <c r="D28" t="n">
-        <v>47.75100070132792</v>
+        <v>7.759537613965787</v>
       </c>
       <c r="E28" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F28" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>35.75063488206492</v>
+        <v>5.809478168335549</v>
       </c>
       <c r="D29" t="n">
-        <v>35.78132556936339</v>
+        <v>5.814465405021551</v>
       </c>
       <c r="E29" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F29" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>46.53179236654047</v>
+        <v>7.561416259562827</v>
       </c>
       <c r="D30" t="n">
-        <v>47.07760025259944</v>
+        <v>7.650110041047409</v>
       </c>
       <c r="E30" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F30" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>43.94253159718827</v>
+        <v>7.140661384543094</v>
       </c>
       <c r="D31" t="n">
-        <v>44.10683989391867</v>
+        <v>7.167361482761785</v>
       </c>
       <c r="E31" t="n">
-        <v>12.96520113611065</v>
+        <v>2.106845184617981</v>
       </c>
       <c r="F31" t="n">
-        <v>13.10143407506558</v>
+        <v>2.128983037198157</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
